--- a/Assets/Document/云熹约定项目文档/11.配音文本/何行舟配音文本.xlsx
+++ b/Assets/Document/云熹约定项目文档/11.配音文本/何行舟配音文本.xlsx
@@ -29,10 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
-  <si>
-    <t>角色分析： 酒吧陪酒人员，他的声音带着刻意的慵懒，但骨子里是对自我命运的无力感。面对女主的解围，他先是本能地戒备、试探，用玩世不恭的态度竖起刺来保护自己。</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>70字</t>
   </si>
@@ -58,7 +55,7 @@
     <t>“赶走了我的大金主……姐姐是在欲擒故纵吗？还是说，你看上了我，想用这种方式让我报答你？”</t>
   </si>
   <si>
-    <t>语速放慢，声音压得更低，带着暧昧的压迫感。“欲擒故纵”“报答”这些词要说得讽刺意味十足，整体语气玩味中带着狠劲，但眼底藏着脆弱和试探。</t>
+    <t>语速放慢，声音压得更低，带着暧昧的压迫感。“欲擒故纵”“报答”这些词要说得讽刺意味十足，整体语气玩味中带着狠劲</t>
   </si>
 </sst>
 </file>
@@ -80,13 +77,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="20"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="20"/>
       <color theme="1"/>
@@ -95,6 +85,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -248,7 +245,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor theme="2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -734,26 +731,23 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1075,44 +1069,43 @@
     <col min="3" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="76.5" spans="1:2">
-      <c r="A1" s="2" t="s">
+    <row r="1" ht="25.5" spans="1:2">
+      <c r="A1" s="2"/>
+      <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+    </row>
+    <row r="2" ht="14.25"/>
+    <row r="3" ht="26.25" spans="1:2">
+      <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" ht="26.25" spans="1:2">
-      <c r="A3" s="4" t="s">
+      <c r="B3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="4" t="s">
+    </row>
+    <row r="4" ht="37.5" spans="1:2">
+      <c r="A4" s="4" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="4" ht="27" spans="1:2">
-      <c r="A4" s="5" t="s">
+      <c r="B4" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="5" t="s">
+    </row>
+    <row r="5" ht="37.5" spans="1:2">
+      <c r="A5" s="4" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="5" ht="27" spans="1:2">
-      <c r="A5" s="5" t="s">
+      <c r="B5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="5" t="s">
+    </row>
+    <row r="6" ht="38.25" spans="1:2">
+      <c r="A6" s="5" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="6" ht="27.75" spans="1:2">
-      <c r="A6" s="6" t="s">
+      <c r="B6" s="5" t="s">
         <v>8</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>9</v>
       </c>
     </row>
   </sheetData>
